--- a/data/trans_orig/IQ19B_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_M-Estudios-trans_orig.xlsx
@@ -7020,7 +7020,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22284</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>26311</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -8540,12 +8540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -8651,12 +8651,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>461</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -9428,12 +9428,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61775</t>
+          <t>62102</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73783</t>
+          <t>74048</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>78950</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92908</t>
+          <t>92814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>145642</t>
+          <t>145820</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -9878,12 +9878,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24646</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>33150</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>45489</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -11216,12 +11216,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11301,12 +11301,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -11327,12 +11327,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11377,12 +11377,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -11549,12 +11549,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11564,12 +11564,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11619,12 +11619,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11634,12 +11634,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -11660,12 +11660,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>462</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>101404</t>
+          <t>101748</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>116985</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>107073</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>123995</t>
+          <t>124282</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>213893</t>
+          <t>213678</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>237512</t>
+          <t>237679</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -14006,12 +14006,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14021,12 +14021,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14041,12 +14041,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14056,12 +14056,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>26518</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14091,12 +14091,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -14345,12 +14345,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14415,12 +14415,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>763</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -14456,12 +14456,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14471,12 +14471,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -14491,12 +14491,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14506,12 +14506,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -14567,12 +14567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14617,12 +14617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14652,12 +14652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -14678,12 +14678,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14693,12 +14693,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14728,12 +14728,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14748,12 +14748,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22129</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -14789,12 +14789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14804,12 +14804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -15455,12 +15455,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>67339</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83005</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15470,12 +15470,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15490,12 +15490,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>82910</t>
+          <t>81720</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97094</t>
+          <t>97396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15505,12 +15505,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15525,12 +15525,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154590</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>176591</t>
+          <t>176900</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15975,12 +15975,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15990,12 +15990,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -16016,12 +16016,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16031,12 +16031,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -16086,12 +16086,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -16238,12 +16238,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16273,12 +16273,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16288,12 +16288,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16308,12 +16308,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16323,12 +16323,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -16828,12 +16828,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -16904,12 +16904,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>16704</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>25927</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -16939,12 +16939,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -16954,12 +16954,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -16974,12 +16974,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>46623</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -16989,12 +16989,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -17243,12 +17243,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -17258,12 +17258,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -17278,12 +17278,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -17313,12 +17313,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -17328,12 +17328,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -17354,12 +17354,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -17369,12 +17369,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -17389,12 +17389,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -17404,12 +17404,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -17424,12 +17424,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -17439,12 +17439,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -17465,12 +17465,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -17480,12 +17480,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -17500,12 +17500,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -17515,12 +17515,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -17535,12 +17535,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -17550,12 +17550,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -17576,12 +17576,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -17591,12 +17591,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -17611,12 +17611,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -17626,12 +17626,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17646,12 +17646,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17661,12 +17661,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17722,12 +17722,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17737,12 +17737,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17757,12 +17757,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17772,12 +17772,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -18020,12 +18020,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -18201,12 +18201,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -18277,12 +18277,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -18292,12 +18292,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -18353,12 +18353,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>98929</t>
+          <t>99802</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>117694</t>
+          <t>118184</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -18368,12 +18368,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -18388,12 +18388,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111909</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>130236</t>
+          <t>130364</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -18403,12 +18403,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -18423,12 +18423,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>216039</t>
+          <t>217414</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>241685</t>
+          <t>243293</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -18438,12 +18438,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -19104,12 +19104,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -19230,12 +19230,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -19346,7 +19346,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -19372,7 +19372,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -19407,7 +19407,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -19437,12 +19437,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -19452,12 +19452,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -19705,7 +19705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -20033,12 +20033,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -20048,12 +20048,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -20068,12 +20068,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -20103,12 +20103,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16715</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>30685</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -20118,12 +20118,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -20372,12 +20372,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -20407,12 +20407,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -20422,12 +20422,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -20442,12 +20442,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -20457,12 +20457,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -20483,12 +20483,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -20498,12 +20498,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -20518,12 +20518,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -20533,12 +20533,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -20553,12 +20553,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -20594,12 +20594,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -20609,12 +20609,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -20629,12 +20629,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -20644,12 +20644,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -20664,12 +20664,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30902</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -20679,12 +20679,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -20705,12 +20705,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -20720,12 +20720,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -20740,12 +20740,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -20775,12 +20775,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -20790,12 +20790,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -20816,12 +20816,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -20831,12 +20831,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -20851,12 +20851,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -20886,12 +20886,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31054</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -20901,12 +20901,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -20927,12 +20927,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -20942,12 +20942,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -20962,12 +20962,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>405</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -20997,12 +20997,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -21012,12 +21012,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -21043,7 +21043,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>965</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -21149,12 +21149,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -21164,12 +21164,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -21184,12 +21184,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -21199,12 +21199,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -21219,12 +21219,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -21234,12 +21234,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -21260,12 +21260,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -21295,12 +21295,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -21310,12 +21310,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -21330,12 +21330,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -21345,12 +21345,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -21482,12 +21482,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71554</t>
+          <t>72230</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>91282</t>
+          <t>91648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -21497,12 +21497,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -21517,12 +21517,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92273</t>
+          <t>91748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>115808</t>
+          <t>114936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -21532,12 +21532,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -21552,12 +21552,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>169013</t>
+          <t>169363</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>199054</t>
+          <t>199880</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -21567,12 +21567,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -21795,12 +21795,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -21826,7 +21826,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -21841,7 +21841,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -21856,12 +21856,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -21871,12 +21871,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -21891,12 +21891,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -21932,12 +21932,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -21947,12 +21947,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -21967,12 +21967,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -21982,12 +21982,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -22002,12 +22002,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -22017,12 +22017,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -22043,12 +22043,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -22058,12 +22058,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -22078,12 +22078,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -22093,12 +22093,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -22113,12 +22113,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -22128,12 +22128,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -22154,12 +22154,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -22169,12 +22169,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -22189,12 +22189,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -22204,12 +22204,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -22224,12 +22224,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -22239,12 +22239,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -22265,12 +22265,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -22280,12 +22280,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -22300,12 +22300,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -22335,12 +22335,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -22350,12 +22350,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -22527,7 +22527,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -22557,12 +22557,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -22572,12 +22572,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -22744,12 +22744,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -22759,12 +22759,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -22779,12 +22779,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -22946,12 +22946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -22966,12 +22966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -22981,12 +22981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -23001,12 +23001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -23016,12 +23016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -23164,7 +23164,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -23214,7 +23214,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -23229,12 +23229,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -23270,12 +23270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -23305,12 +23305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -23320,12 +23320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -23340,12 +23340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -23355,12 +23355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -23396,12 +23396,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -23416,12 +23416,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -23431,12 +23431,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -23451,12 +23451,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -23466,12 +23466,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -23492,12 +23492,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -23507,12 +23507,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -23527,12 +23527,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -23542,12 +23542,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -23577,12 +23577,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -23603,12 +23603,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -23618,12 +23618,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -23638,12 +23638,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -23653,12 +23653,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -23673,12 +23673,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -23688,12 +23688,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -23714,12 +23714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -23729,12 +23729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -23764,12 +23764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -23784,12 +23784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -23799,12 +23799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -23825,12 +23825,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -23860,12 +23860,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>825</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -23875,12 +23875,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -23895,12 +23895,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -23910,12 +23910,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -23941,7 +23941,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -23971,12 +23971,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -23986,12 +23986,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -24006,12 +24006,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -24047,12 +24047,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -24062,12 +24062,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -24082,12 +24082,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -24097,12 +24097,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -24117,12 +24117,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>21851</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -24132,12 +24132,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -24158,12 +24158,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -24173,12 +24173,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -24193,12 +24193,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -24208,12 +24208,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -24228,12 +24228,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -24269,12 +24269,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -24284,12 +24284,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -24339,12 +24339,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -24354,12 +24354,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24380,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>104391</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>128525</t>
+          <t>129327</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -24395,12 +24395,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -24415,12 +24415,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>129618</t>
+          <t>129138</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>156970</t>
+          <t>157613</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -24430,12 +24430,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -24450,12 +24450,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>241035</t>
+          <t>238816</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>280846</t>
+          <t>278178</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -24465,12 +24465,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
